--- a/Data/FlightPlan/FPL_11OCT26.xlsx
+++ b/Data/FlightPlan/FPL_11OCT26.xlsx
@@ -443,6 +443,12 @@
     <t>11:05</t>
   </si>
   <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
     <t>13:30</t>
   </si>
   <si>
@@ -533,9 +539,6 @@
     <t>HKT</t>
   </si>
   <si>
-    <t>08:50</t>
-  </si>
-  <si>
     <t>CXR</t>
   </si>
   <si>
@@ -887,42 +890,42 @@
     <t>VN-A642</t>
   </si>
   <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
     <t>SAI</t>
   </si>
   <si>
     <t>21:20</t>
   </si>
   <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
     <t>VN-A646</t>
   </si>
   <si>
@@ -986,9 +989,6 @@
     <t>07:10</t>
   </si>
   <si>
-    <t>11:45</t>
-  </si>
-  <si>
     <t>13:55</t>
   </si>
   <si>
@@ -1208,7 +1208,7 @@
     <t>Total Record(s): 374</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 10, 2026 21:40</t>
+    <t xml:space="preserve">Generated on  Oct 11, 2026 00:39</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3880,9 +3880,13 @@
       <c t="s" r="J77" s="7">
         <v>143</v>
       </c>
-      <c r="K77" s="7"/>
+      <c t="s" r="K77" s="7">
+        <v>144</v>
+      </c>
       <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
+      <c t="s" r="M77" s="7">
+        <v>145</v>
+      </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c t="s" r="A78" s="6">
@@ -3908,7 +3912,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>137</v>
@@ -3944,7 +3948,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -3989,10 +3993,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4010,7 +4014,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4022,10 +4026,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4058,7 +4062,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4076,7 +4080,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4109,7 +4113,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4121,10 +4125,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4157,7 +4161,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4169,10 +4173,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4190,7 +4194,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4202,10 +4206,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4235,7 +4239,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>100</v>
@@ -4256,7 +4260,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4268,7 +4272,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>138</v>
@@ -4289,7 +4293,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4301,7 +4305,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>139</v>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4334,10 +4338,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4370,7 +4374,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4379,13 +4383,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4403,13 +4407,13 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>20</v>
@@ -4418,7 +4422,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4436,7 +4440,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4448,10 +4452,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4484,7 +4488,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4502,7 +4506,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4514,10 +4518,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4535,7 +4539,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4547,10 +4551,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4583,7 +4587,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4592,13 +4596,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4616,13 +4620,13 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>20</v>
@@ -4649,7 +4653,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4658,10 +4662,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>27</v>
@@ -4678,17 +4682,17 @@
         <v>7614</v>
       </c>
       <c t="s" r="C104" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>58</v>
@@ -4697,7 +4701,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4711,11 +4715,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C105" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4724,13 +4728,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="I105" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4763,7 +4767,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4772,10 +4776,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>115</v>
@@ -4796,19 +4800,19 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>137</v>
@@ -4829,7 +4833,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4877,7 +4881,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4889,7 +4893,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>39</v>
@@ -4910,7 +4914,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4919,13 +4923,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4943,13 +4947,13 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>58</v>
@@ -4976,7 +4980,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5024,7 +5028,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5039,7 +5043,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5057,7 +5061,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5069,7 +5073,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>93</v>
@@ -5090,7 +5094,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5102,10 +5106,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5123,7 +5127,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5132,10 +5136,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>21</v>
@@ -5167,11 +5171,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C121" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5180,13 +5184,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5204,22 +5208,22 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5252,7 +5256,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5261,10 +5265,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>96</v>
@@ -5285,13 +5289,13 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>58</v>
@@ -5300,7 +5304,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5318,7 +5322,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5327,7 +5331,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>117</v>
@@ -5351,22 +5355,22 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5399,7 +5403,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5411,7 +5415,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>36</v>
@@ -5432,7 +5436,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5444,10 +5448,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5465,7 +5469,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5477,7 +5481,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>116</v>
@@ -5498,7 +5502,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5513,7 +5517,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5531,7 +5535,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5540,13 +5544,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I133" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5564,22 +5568,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5608,11 +5612,11 @@
         <v>2983</v>
       </c>
       <c t="s" r="C136" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5624,10 +5628,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5645,7 +5649,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5678,7 +5682,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5711,7 +5715,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5726,7 +5730,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5755,11 +5759,11 @@
         <v>35</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5768,10 +5772,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>85</v>
@@ -5807,22 +5811,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5840,7 +5844,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5849,13 +5853,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="I144" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5888,7 +5892,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5897,10 +5901,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>22</v>
@@ -5921,19 +5925,19 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>111</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>125</v>
@@ -5954,7 +5958,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5963,13 +5967,13 @@
         <v>111</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -5987,13 +5991,13 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>20</v>
@@ -6002,7 +6006,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6020,7 +6024,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6029,10 +6033,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>87</v>
@@ -6053,22 +6057,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6101,7 +6105,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6113,10 +6117,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6134,7 +6138,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6149,7 +6153,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6167,7 +6171,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6182,7 +6186,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6200,7 +6204,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6212,7 +6216,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>114</v>
@@ -6233,7 +6237,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6242,10 +6246,10 @@
         <v>128</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>72</v>
@@ -6266,22 +6270,22 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>128</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6299,7 +6303,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6308,20 +6312,20 @@
         <v>128</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I159" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="K159" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6336,13 +6340,13 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>128</v>
@@ -6351,14 +6355,14 @@
         <v>99</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="K160" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -6373,7 +6377,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6391,11 +6395,11 @@
         <v>104</v>
       </c>
       <c t="s" r="K161" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6410,7 +6414,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6425,7 +6429,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6458,7 +6462,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6467,7 +6471,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>66</v>
@@ -6491,19 +6495,19 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>47</v>
@@ -6524,7 +6528,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6536,10 +6540,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6557,7 +6561,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6590,7 +6594,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6602,7 +6606,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>61</v>
@@ -6623,7 +6627,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6635,7 +6639,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>103</v>
@@ -6656,7 +6660,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6668,10 +6672,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6689,7 +6693,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6701,10 +6705,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6737,7 +6741,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6749,10 +6753,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6770,7 +6774,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6785,7 +6789,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6803,7 +6807,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6812,7 +6816,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I175" s="7">
         <v>59</v>
@@ -6836,13 +6840,13 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>58</v>
@@ -6869,7 +6873,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6881,10 +6885,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6917,7 +6921,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6929,10 +6933,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6950,7 +6954,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6962,10 +6966,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6983,7 +6987,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6995,10 +6999,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7016,7 +7020,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7049,7 +7053,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7058,10 +7062,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>59</v>
@@ -7082,19 +7086,19 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>101</v>
@@ -7115,7 +7119,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7127,10 +7131,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7148,7 +7152,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7160,10 +7164,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7196,7 +7200,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7211,7 +7215,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7229,7 +7233,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7241,10 +7245,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7262,7 +7266,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7295,7 +7299,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7307,10 +7311,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7328,7 +7332,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7337,13 +7341,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7361,22 +7365,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
+        <v>265</v>
+      </c>
+      <c r="F193" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G193" s="8">
+        <v>259</v>
+      </c>
+      <c t="s" r="H193" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I193" s="7">
+        <v>267</v>
+      </c>
+      <c t="s" r="J193" s="7">
         <v>264</v>
-      </c>
-      <c r="F193" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G193" s="8">
-        <v>258</v>
-      </c>
-      <c t="s" r="H193" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I193" s="7">
-        <v>266</v>
-      </c>
-      <c t="s" r="J193" s="7">
-        <v>263</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7409,7 +7413,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7421,10 +7425,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7442,7 +7446,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7457,7 +7461,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7475,7 +7479,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7508,7 +7512,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7520,10 +7524,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7541,7 +7545,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7553,10 +7557,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7574,7 +7578,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7583,13 +7587,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7607,22 +7611,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7655,7 +7659,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7664,10 +7668,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>142</v>
@@ -7688,22 +7692,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7721,7 +7725,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7730,13 +7734,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7754,19 +7758,19 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>116</v>
@@ -7787,7 +7791,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7796,13 +7800,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>127</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7820,22 +7824,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7853,7 +7857,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7865,10 +7869,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7901,7 +7905,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7913,10 +7917,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7934,7 +7938,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7949,7 +7953,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7967,7 +7971,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7979,10 +7983,10 @@
         <v>122</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8000,7 +8004,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8033,7 +8037,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8048,7 +8052,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8066,7 +8070,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8078,10 +8082,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8099,7 +8103,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8108,10 +8112,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>62</v>
@@ -8132,13 +8136,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>58</v>
@@ -8180,7 +8184,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8195,7 +8199,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8213,7 +8217,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8228,7 +8232,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8246,7 +8250,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8258,10 +8262,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8279,7 +8283,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8294,7 +8298,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8327,7 +8331,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8336,13 +8340,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8360,13 +8364,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>58</v>
@@ -8393,7 +8397,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8402,13 +8406,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8426,13 +8430,13 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>58</v>
@@ -8459,7 +8463,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8474,7 +8478,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8492,7 +8496,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8504,7 +8508,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>139</v>
@@ -8533,14 +8537,14 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>901</v>
+        <v>127</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8549,13 +8553,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>96</v>
+        <v>293</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8566,29 +8570,29 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>902</v>
+        <v>634</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8599,29 +8603,29 @@
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>913</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
+        <v>128</v>
+      </c>
+      <c t="s" r="H234" s="8">
         <v>58</v>
       </c>
-      <c t="s" r="H234" s="8">
-        <v>292</v>
-      </c>
       <c t="s" r="I234" s="7">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8632,78 +8636,78 @@
         <v>13</v>
       </c>
       <c r="B235" s="7">
-        <v>914</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>292</v>
+        <v>58</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="6"/>
-      <c r="B236" s="7"/>
-      <c r="C236" s="7"/>
+      <c t="s" r="A236" s="6">
+        <v>13</v>
+      </c>
+      <c r="B236" s="7">
+        <v>637</v>
+      </c>
+      <c t="s" r="C236" s="7">
+        <v>14</v>
+      </c>
       <c r="D236" s="7"/>
-      <c r="E236" s="7"/>
-      <c r="F236" s="7"/>
-      <c r="G236" s="8"/>
-      <c r="H236" s="8"/>
-      <c r="I236" s="7"/>
-      <c r="J236" s="7"/>
+      <c t="s" r="E236" s="7">
+        <v>292</v>
+      </c>
+      <c r="F236" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G236" s="8">
+        <v>128</v>
+      </c>
+      <c t="s" r="H236" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I236" s="7">
+        <v>161</v>
+      </c>
+      <c t="s" r="J236" s="7">
+        <v>200</v>
+      </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c r="M236" s="7"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
-      <c t="s" r="A237" s="6">
-        <v>13</v>
-      </c>
-      <c r="B237" s="7">
-        <v>339</v>
-      </c>
-      <c t="s" r="C237" s="7">
-        <v>14</v>
-      </c>
+      <c r="A237" s="6"/>
+      <c r="B237" s="7"/>
+      <c r="C237" s="7"/>
       <c r="D237" s="7"/>
-      <c t="s" r="E237" s="7">
-        <v>294</v>
-      </c>
-      <c r="F237" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G237" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H237" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I237" s="7">
-        <v>77</v>
-      </c>
-      <c t="s" r="J237" s="7">
-        <v>174</v>
-      </c>
+      <c r="E237" s="7"/>
+      <c r="F237" s="7"/>
+      <c r="G237" s="8"/>
+      <c r="H237" s="8"/>
+      <c r="I237" s="7"/>
+      <c r="J237" s="7"/>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c r="M237" s="7"/>
@@ -8713,7 +8717,7 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>718</v>
+        <v>339</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
@@ -8726,16 +8730,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H238" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H238" s="8">
-        <v>128</v>
-      </c>
       <c t="s" r="I238" s="7">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8746,7 +8750,7 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
@@ -8759,16 +8763,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H239" s="8">
         <v>128</v>
       </c>
-      <c t="s" r="H239" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I239" s="7">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8779,7 +8783,7 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>452</v>
+        <v>719</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
@@ -8792,16 +8796,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
+        <v>128</v>
+      </c>
+      <c t="s" r="H240" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H240" s="8">
-        <v>58</v>
-      </c>
       <c t="s" r="I240" s="7">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>284</v>
+        <v>207</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8812,7 +8816,7 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
@@ -8825,16 +8829,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H241" s="8">
         <v>58</v>
       </c>
-      <c t="s" r="H241" s="8">
-        <v>218</v>
-      </c>
       <c t="s" r="I241" s="7">
-        <v>187</v>
+        <v>98</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8845,7 +8849,7 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
@@ -8858,65 +8862,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="6"/>
-      <c r="B243" s="7"/>
-      <c r="C243" s="7"/>
+      <c t="s" r="A243" s="6">
+        <v>13</v>
+      </c>
+      <c r="B243" s="7">
+        <v>466</v>
+      </c>
+      <c t="s" r="C243" s="7">
+        <v>14</v>
+      </c>
       <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7"/>
-      <c r="G243" s="8"/>
-      <c r="H243" s="8"/>
-      <c r="I243" s="7"/>
-      <c r="J243" s="7"/>
+      <c t="s" r="E243" s="7">
+        <v>294</v>
+      </c>
+      <c r="F243" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G243" s="8">
+        <v>219</v>
+      </c>
+      <c t="s" r="H243" s="8">
+        <v>58</v>
+      </c>
+      <c t="s" r="I243" s="7">
+        <v>29</v>
+      </c>
+      <c t="s" r="J243" s="7">
+        <v>295</v>
+      </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c t="s" r="A244" s="6">
-        <v>13</v>
-      </c>
-      <c r="B244" s="7">
-        <v>989</v>
-      </c>
-      <c t="s" r="C244" s="7">
-        <v>14</v>
-      </c>
+      <c r="A244" s="6"/>
+      <c r="B244" s="7"/>
+      <c r="C244" s="7"/>
       <c r="D244" s="7"/>
-      <c t="s" r="E244" s="7">
-        <v>296</v>
-      </c>
-      <c r="F244" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G244" s="8">
-        <v>64</v>
-      </c>
-      <c t="s" r="H244" s="8">
-        <v>128</v>
-      </c>
-      <c t="s" r="I244" s="7">
-        <v>297</v>
-      </c>
-      <c t="s" r="J244" s="7">
-        <v>183</v>
-      </c>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
+      <c r="G244" s="8"/>
+      <c r="H244" s="8"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="7"/>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
@@ -8926,7 +8930,7 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>973</v>
+        <v>989</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
@@ -8939,16 +8943,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="H245" s="8">
         <v>128</v>
       </c>
-      <c t="s" r="H245" s="8">
-        <v>81</v>
-      </c>
       <c t="s" r="I245" s="7">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8959,7 +8963,7 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>814</v>
+        <v>973</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
@@ -8972,16 +8976,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
+        <v>128</v>
+      </c>
+      <c t="s" r="H246" s="8">
         <v>81</v>
       </c>
-      <c t="s" r="H246" s="8">
-        <v>20</v>
-      </c>
       <c t="s" r="I246" s="7">
-        <v>166</v>
+        <v>290</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8992,7 +8996,7 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>3908</v>
+        <v>814</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
@@ -9005,16 +9009,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9022,10 +9026,10 @@
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c t="s" r="A248" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
@@ -9038,65 +9042,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H248" s="8">
         <v>298</v>
       </c>
-      <c t="s" r="H248" s="8">
-        <v>20</v>
-      </c>
       <c t="s" r="I248" s="7">
-        <v>300</v>
+        <v>191</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c r="A249" s="6"/>
-      <c r="B249" s="7"/>
-      <c r="C249" s="7"/>
+      <c t="s" r="A249" s="6">
+        <v>31</v>
+      </c>
+      <c r="B249" s="7">
+        <v>3909</v>
+      </c>
+      <c t="s" r="C249" s="7">
+        <v>14</v>
+      </c>
       <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
-      <c r="G249" s="8"/>
-      <c r="H249" s="8"/>
-      <c r="I249" s="7"/>
-      <c r="J249" s="7"/>
+      <c t="s" r="E249" s="7">
+        <v>296</v>
+      </c>
+      <c r="F249" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G249" s="8">
+        <v>298</v>
+      </c>
+      <c t="s" r="H249" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I249" s="7">
+        <v>300</v>
+      </c>
+      <c t="s" r="J249" s="7">
+        <v>301</v>
+      </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c t="s" r="A250" s="6">
-        <v>13</v>
-      </c>
-      <c r="B250" s="7">
-        <v>127</v>
-      </c>
-      <c t="s" r="C250" s="7">
-        <v>14</v>
-      </c>
+      <c r="A250" s="6"/>
+      <c r="B250" s="7"/>
+      <c r="C250" s="7"/>
       <c r="D250" s="7"/>
-      <c t="s" r="E250" s="7">
-        <v>302</v>
-      </c>
-      <c r="F250" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G250" s="8">
-        <v>58</v>
-      </c>
-      <c t="s" r="H250" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I250" s="7">
-        <v>142</v>
-      </c>
-      <c t="s" r="J250" s="7">
-        <v>303</v>
-      </c>
+      <c r="E250" s="7"/>
+      <c r="F250" s="7"/>
+      <c r="G250" s="8"/>
+      <c r="H250" s="8"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="7"/>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
@@ -9106,7 +9110,7 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>634</v>
+        <v>901</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
@@ -9119,16 +9123,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9139,7 +9143,7 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>1504</v>
+        <v>902</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
@@ -9152,16 +9156,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9172,7 +9176,7 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>1505</v>
+        <v>913</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
@@ -9188,13 +9192,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>128</v>
+        <v>303</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9205,7 +9209,7 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>637</v>
+        <v>914</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
@@ -9218,16 +9222,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>128</v>
+        <v>303</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9260,7 +9264,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9272,10 +9276,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9293,7 +9297,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9302,13 +9306,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9326,13 +9330,13 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>20</v>
@@ -9341,7 +9345,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9359,7 +9363,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9374,7 +9378,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9407,7 +9411,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9422,7 +9426,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9440,7 +9444,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9452,10 +9456,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9473,7 +9477,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9485,10 +9489,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9506,7 +9510,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9539,7 +9543,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9548,13 +9552,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9572,22 +9576,22 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9620,7 +9624,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9632,7 +9636,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>44</v>
@@ -9653,7 +9657,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9662,10 +9666,10 @@
         <v>128</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>72</v>
@@ -9686,13 +9690,13 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>128</v>
@@ -9701,7 +9705,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9719,7 +9723,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9728,13 +9732,13 @@
         <v>128</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9752,22 +9756,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>128</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9800,7 +9804,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9809,7 +9813,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>22</v>
@@ -9833,22 +9837,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9866,7 +9870,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9878,10 +9882,10 @@
         <v>122</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9899,7 +9903,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9911,10 +9915,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9947,7 +9951,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -9980,7 +9984,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -9992,7 +9996,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>39</v>
@@ -10013,7 +10017,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10046,7 +10050,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10061,7 +10065,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10079,7 +10083,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10094,7 +10098,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10112,7 +10116,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10127,7 +10131,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10160,7 +10164,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10169,13 +10173,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10193,22 +10197,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10226,7 +10230,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10238,7 +10242,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>325</v>
+        <v>145</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>326</v>
@@ -10259,7 +10263,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10271,10 +10275,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10292,7 +10296,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10307,7 +10311,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10325,7 +10329,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10340,7 +10344,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10358,7 +10362,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10370,10 +10374,10 @@
         <v>298</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10391,7 +10395,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10403,7 +10407,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>327</v>
@@ -10481,13 +10485,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10511,7 +10515,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>58</v>
@@ -10553,7 +10557,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10586,7 +10590,7 @@
         <v>332</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10631,10 +10635,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10667,7 +10671,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10697,10 +10701,10 @@
         <v>122</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10730,10 +10734,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10763,10 +10767,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10829,7 +10833,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>93</v>
@@ -10862,10 +10866,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10895,7 +10899,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>334</v>
@@ -10940,13 +10944,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10970,16 +10974,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>97</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11006,10 +11010,10 @@
         <v>97</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>25</v>
@@ -11036,7 +11040,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>58</v>
@@ -11075,10 +11079,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11111,7 +11115,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11153,10 +11157,10 @@
         <v>64</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>49</v>
@@ -11183,7 +11187,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>337</v>
@@ -11219,10 +11223,10 @@
         <v>337</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>65</v>
@@ -11249,16 +11253,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>64</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11303,7 +11307,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>52</v>
@@ -11417,10 +11421,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11483,10 +11487,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11519,7 +11523,7 @@
         <v>341</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11567,7 +11571,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11597,7 +11601,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>115</v>
@@ -11666,7 +11670,7 @@
         <v>331</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11711,10 +11715,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11744,10 +11748,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11780,7 +11784,7 @@
         <v>344</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11807,7 +11811,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>98</v>
@@ -11837,7 +11841,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>58</v>
@@ -11876,10 +11880,10 @@
         <v>345</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11990,10 +11994,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12023,10 +12027,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12059,7 +12063,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12089,7 +12093,7 @@
         <v>350</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>117</v>
@@ -12125,7 +12129,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12203,10 +12207,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12314,10 +12318,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>49</v>
@@ -12344,16 +12348,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12415,7 +12419,7 @@
         <v>9854</v>
       </c>
       <c t="s" r="C361" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
@@ -12425,7 +12429,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>20</v>
@@ -12434,7 +12438,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12476,7 +12480,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>361</v>
@@ -12506,7 +12510,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>58</v>
@@ -12515,7 +12519,7 @@
         <v>362</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12542,10 +12546,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>114</v>
@@ -12572,7 +12576,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>58</v>
@@ -12581,7 +12585,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12644,10 +12648,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12692,10 +12696,10 @@
         <v>81</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12728,7 +12732,7 @@
         <v>364</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12758,7 +12762,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>73</v>
@@ -12794,7 +12798,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12905,10 +12909,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12938,7 +12942,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>88</v>
@@ -13022,7 +13026,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13052,10 +13056,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13115,13 +13119,13 @@
         <v>111</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13145,7 +13149,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>111</v>
@@ -13154,7 +13158,7 @@
         <v>331</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13268,7 +13272,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13298,7 +13302,7 @@
         <v>354</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>53</v>
@@ -13412,7 +13416,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>370</v>
@@ -13448,7 +13452,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13481,7 +13485,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13511,10 +13515,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13547,7 +13551,7 @@
         <v>374</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13577,10 +13581,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13610,10 +13614,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13691,7 +13695,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>96</v>
@@ -13721,13 +13725,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13751,16 +13755,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13793,7 +13797,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13826,7 +13830,7 @@
         <v>341</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13868,13 +13872,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13898,16 +13902,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13970,7 +13974,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>85</v>
@@ -14006,7 +14010,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14084,10 +14088,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14168,7 +14172,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14198,10 +14202,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14267,7 +14271,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14294,13 +14298,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14324,13 +14328,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>87</v>
@@ -14411,7 +14415,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>21</v>
@@ -14444,10 +14448,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14477,7 +14481,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>124</v>
@@ -14510,7 +14514,7 @@
         <v>350</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>90</v>
@@ -14543,10 +14547,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14609,10 +14613,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14654,13 +14658,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I435" s="7">
         <v>112</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14684,7 +14688,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>384</v>
@@ -14693,7 +14697,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14720,10 +14724,10 @@
         <v>384</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>385</v>
@@ -14774,7 +14778,7 @@
         <v>364</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14804,10 +14808,10 @@
         <v>387</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14846,7 +14850,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>389</v>
@@ -14882,10 +14886,10 @@
         <v>389</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>390</v>
@@ -14917,7 +14921,7 @@
         <v>664</v>
       </c>
       <c t="s" r="C445" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
@@ -14930,13 +14934,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -14960,13 +14964,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>39</v>
@@ -14999,10 +15003,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15035,7 +15039,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15080,7 +15084,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>59</v>

--- a/Data/FlightPlan/FPL_11OCT26.xlsx
+++ b/Data/FlightPlan/FPL_11OCT26.xlsx
@@ -788,7 +788,7 @@
     <t>VN-A629</t>
   </si>
   <si>
-    <t>12:27</t>
+    <t>12:26</t>
   </si>
   <si>
     <t>14:45</t>
@@ -854,7 +854,7 @@
     <t>09:14</t>
   </si>
   <si>
-    <t>13:29</t>
+    <t>13:44</t>
   </si>
   <si>
     <t>16:35</t>
@@ -971,7 +971,7 @@
     <t>10:06</t>
   </si>
   <si>
-    <t>12:47</t>
+    <t>12:54</t>
   </si>
   <si>
     <t>VTE</t>
@@ -1136,9 +1136,6 @@
     <t>FSZ</t>
   </si>
   <si>
-    <t>13:44</t>
-  </si>
-  <si>
     <t>17:10</t>
   </si>
   <si>
@@ -1154,6 +1151,9 @@
     <t>08:23</t>
   </si>
   <si>
+    <t>12:04</t>
+  </si>
+  <si>
     <t>01:35</t>
   </si>
   <si>
@@ -1235,9 +1235,6 @@
     <t>21:40</t>
   </si>
   <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
     <t>VN-A675</t>
   </si>
   <si>
@@ -1250,6 +1247,9 @@
     <t>10:23</t>
   </si>
   <si>
+    <t>13:19</t>
+  </si>
+  <si>
     <t>VN-A677</t>
   </si>
   <si>
@@ -1382,10 +1382,10 @@
     <t>MEL</t>
   </si>
   <si>
-    <t>Total Record(s): 374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated on  Oct 11, 2026 10:45</t>
+    <t>Total Record(s): 373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated on  Oct 11, 2026 11:07</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3729,7 +3729,9 @@
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
+      <c t="s" r="M65" s="7">
+        <v>96</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c t="s" r="A66" s="6">
@@ -7411,7 +7413,9 @@
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
-      <c r="M185" s="7"/>
+      <c t="s" r="M185" s="7">
+        <v>82</v>
+      </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c t="s" r="A186" s="6">
@@ -7842,7 +7846,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -10917,7 +10921,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>375</v>
+        <v>281</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10977,7 +10981,7 @@
         <v>67</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>105</v>
@@ -11043,7 +11047,7 @@
         <v>67</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>214</v>
@@ -11079,7 +11083,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11099,7 +11103,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11114,7 +11118,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11134,7 +11138,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11149,7 +11153,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11184,7 +11188,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11203,7 +11207,9 @@
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
-      <c r="M307" s="7"/>
+      <c t="s" r="M307" s="7">
+        <v>380</v>
+      </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
       <c t="s" r="A308" s="6">
@@ -11217,7 +11223,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11250,7 +11256,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11283,7 +11289,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11316,7 +11322,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11349,7 +11355,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -12860,62 +12866,84 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>9854</v>
+        <v>771</v>
       </c>
       <c t="s" r="C362" s="7">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
         <v>408</v>
       </c>
       <c r="F362" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>219</v>
+        <v>67</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
-      <c r="M362" s="7"/>
+      <c t="s" r="M362" s="7">
+        <v>88</v>
+      </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
-      <c r="A363" s="6"/>
-      <c r="B363" s="7"/>
-      <c r="C363" s="7"/>
+      <c t="s" r="A363" s="6">
+        <v>13</v>
+      </c>
+      <c r="B363" s="7">
+        <v>770</v>
+      </c>
+      <c t="s" r="C363" s="7">
+        <v>14</v>
+      </c>
       <c r="D363" s="7"/>
-      <c r="E363" s="7"/>
-      <c r="F363" s="7"/>
-      <c r="G363" s="8"/>
-      <c r="H363" s="8"/>
-      <c r="I363" s="7"/>
-      <c r="J363" s="7"/>
+      <c t="s" r="E363" s="7">
+        <v>408</v>
+      </c>
+      <c r="F363" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G363" s="8">
+        <v>193</v>
+      </c>
+      <c t="s" r="H363" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="I363" s="7">
+        <v>410</v>
+      </c>
+      <c t="s" r="J363" s="7">
+        <v>228</v>
+      </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
-      <c r="M363" s="7"/>
+      <c t="s" r="M363" s="7">
+        <v>411</v>
+      </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
       <c t="s" r="A364" s="6">
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>771</v>
+        <v>463</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12924,18 +12952,20 @@
         <v>67</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>19</v>
-      </c>
-      <c r="K364" s="7"/>
+        <v>124</v>
+      </c>
+      <c t="s" r="K364" s="7">
+        <v>296</v>
+      </c>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>88</v>
+        <v>412</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -12943,34 +12973,36 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>770</v>
+        <v>464</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>67</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>411</v>
+        <v>109</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>228</v>
-      </c>
-      <c r="K365" s="7"/>
+        <v>57</v>
+      </c>
+      <c t="s" r="K365" s="7">
+        <v>270</v>
+      </c>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>412</v>
+        <v>202</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -12978,14 +13010,14 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>463</v>
+        <v>567</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12994,20 +13026,20 @@
         <v>67</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>344</v>
+        <v>84</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>124</v>
+        <v>375</v>
       </c>
       <c t="s" r="K366" s="7">
-        <v>296</v>
+        <v>353</v>
       </c>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>147</v>
+        <v>375</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13015,129 +13047,125 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>464</v>
+        <v>568</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>67</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>109</v>
+        <v>361</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>57</v>
-      </c>
-      <c t="s" r="K367" s="7">
-        <v>270</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="K367" s="7"/>
       <c r="L367" s="7"/>
-      <c t="s" r="M367" s="7">
-        <v>202</v>
-      </c>
+      <c r="M367" s="7"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
-      <c t="s" r="A368" s="6">
-        <v>13</v>
-      </c>
-      <c r="B368" s="7">
-        <v>567</v>
-      </c>
-      <c t="s" r="C368" s="7">
-        <v>14</v>
-      </c>
+      <c r="A368" s="6"/>
+      <c r="B368" s="7"/>
+      <c r="C368" s="7"/>
       <c r="D368" s="7"/>
-      <c t="s" r="E368" s="7">
-        <v>409</v>
-      </c>
-      <c r="F368" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G368" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H368" s="8">
-        <v>134</v>
-      </c>
-      <c t="s" r="I368" s="7">
-        <v>84</v>
-      </c>
-      <c t="s" r="J368" s="7">
-        <v>376</v>
-      </c>
-      <c t="s" r="K368" s="7">
-        <v>353</v>
-      </c>
+      <c r="E368" s="7"/>
+      <c r="F368" s="7"/>
+      <c r="G368" s="8"/>
+      <c r="H368" s="8"/>
+      <c r="I368" s="7"/>
+      <c r="J368" s="7"/>
+      <c r="K368" s="7"/>
       <c r="L368" s="7"/>
-      <c t="s" r="M368" s="7">
-        <v>376</v>
-      </c>
+      <c r="M368" s="7"/>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c t="s" r="A369" s="6">
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>568</v>
+        <v>813</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F369" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>71</v>
+        <v>318</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
-      <c r="M369" s="7"/>
+      <c t="s" r="M369" s="7">
+        <v>133</v>
+      </c>
     </row>
     <row r="370" ht="15" customHeight="1">
-      <c r="A370" s="6"/>
-      <c r="B370" s="7"/>
-      <c r="C370" s="7"/>
+      <c t="s" r="A370" s="6">
+        <v>13</v>
+      </c>
+      <c r="B370" s="7">
+        <v>970</v>
+      </c>
+      <c t="s" r="C370" s="7">
+        <v>14</v>
+      </c>
       <c r="D370" s="7"/>
-      <c r="E370" s="7"/>
-      <c r="F370" s="7"/>
-      <c r="G370" s="8"/>
-      <c r="H370" s="8"/>
-      <c r="I370" s="7"/>
-      <c r="J370" s="7"/>
+      <c t="s" r="E370" s="7">
+        <v>413</v>
+      </c>
+      <c r="F370" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G370" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H370" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="I370" s="7">
+        <v>240</v>
+      </c>
+      <c t="s" r="J370" s="7">
+        <v>309</v>
+      </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
-      <c r="M370" s="7"/>
+      <c t="s" r="M370" s="7">
+        <v>109</v>
+      </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
       <c t="s" r="A371" s="6">
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>813</v>
+        <v>715</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
@@ -13150,29 +13178,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>368</v>
+        <v>414</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c t="s" r="M371" s="7">
-        <v>133</v>
-      </c>
+      <c r="M371" s="7"/>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>970</v>
+        <v>714</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
@@ -13185,29 +13211,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>56</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>240</v>
+        <v>31</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>309</v>
+        <v>222</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
-      <c t="s" r="M372" s="7">
-        <v>109</v>
-      </c>
+      <c r="M372" s="7"/>
     </row>
     <row r="373" ht="14.25" customHeight="1">
       <c t="s" r="A373" s="6">
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>715</v>
+        <v>878</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
@@ -13223,47 +13247,29 @@
         <v>56</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>84</v>
+        <v>247</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c t="s" r="A374" s="6">
-        <v>13</v>
-      </c>
-      <c r="B374" s="7">
-        <v>714</v>
-      </c>
-      <c t="s" r="C374" s="7">
-        <v>14</v>
-      </c>
+      <c r="A374" s="6"/>
+      <c r="B374" s="7"/>
+      <c r="C374" s="7"/>
       <c r="D374" s="7"/>
-      <c t="s" r="E374" s="7">
-        <v>413</v>
-      </c>
-      <c r="F374" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G374" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H374" s="8">
-        <v>56</v>
-      </c>
-      <c t="s" r="I374" s="7">
-        <v>31</v>
-      </c>
-      <c t="s" r="J374" s="7">
-        <v>222</v>
-      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="7"/>
+      <c r="G374" s="8"/>
+      <c r="H374" s="8"/>
+      <c r="I374" s="7"/>
+      <c r="J374" s="7"/>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
@@ -13273,45 +13279,65 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>878</v>
+        <v>961</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>415</v>
+        <v>156</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>247</v>
+        <v>54</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
-      <c r="M375" s="7"/>
+      <c t="s" r="M375" s="7">
+        <v>54</v>
+      </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
-      <c r="A376" s="6"/>
-      <c r="B376" s="7"/>
-      <c r="C376" s="7"/>
+      <c t="s" r="A376" s="6">
+        <v>13</v>
+      </c>
+      <c r="B376" s="7">
+        <v>946</v>
+      </c>
+      <c t="s" r="C376" s="7">
+        <v>14</v>
+      </c>
       <c r="D376" s="7"/>
-      <c r="E376" s="7"/>
-      <c r="F376" s="7"/>
-      <c r="G376" s="8"/>
-      <c r="H376" s="8"/>
-      <c r="I376" s="7"/>
-      <c r="J376" s="7"/>
+      <c t="s" r="E376" s="7">
+        <v>416</v>
+      </c>
+      <c r="F376" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G376" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="H376" s="8">
+        <v>78</v>
+      </c>
+      <c t="s" r="I376" s="7">
+        <v>194</v>
+      </c>
+      <c t="s" r="J376" s="7">
+        <v>208</v>
+      </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c r="M376" s="7"/>
@@ -13321,7 +13347,7 @@
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
@@ -13334,29 +13360,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>67</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>156</v>
+        <v>348</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
-      <c t="s" r="M377" s="7">
-        <v>54</v>
-      </c>
+      <c r="M377" s="7"/>
     </row>
     <row r="378" ht="14.25" customHeight="1">
       <c t="s" r="A378" s="6">
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>946</v>
+        <v>962</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
@@ -13372,47 +13396,29 @@
         <v>67</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>194</v>
+        <v>62</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c r="M378" s="7"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
-      <c t="s" r="A379" s="6">
-        <v>13</v>
-      </c>
-      <c r="B379" s="7">
-        <v>947</v>
-      </c>
-      <c t="s" r="C379" s="7">
-        <v>14</v>
-      </c>
+      <c r="A379" s="6"/>
+      <c r="B379" s="7"/>
+      <c r="C379" s="7"/>
       <c r="D379" s="7"/>
-      <c t="s" r="E379" s="7">
-        <v>416</v>
-      </c>
-      <c r="F379" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G379" s="8">
-        <v>78</v>
-      </c>
-      <c t="s" r="H379" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I379" s="7">
-        <v>348</v>
-      </c>
-      <c t="s" r="J379" s="7">
-        <v>100</v>
-      </c>
+      <c r="E379" s="7"/>
+      <c r="F379" s="7"/>
+      <c r="G379" s="8"/>
+      <c r="H379" s="8"/>
+      <c r="I379" s="7"/>
+      <c r="J379" s="7"/>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c r="M379" s="7"/>
@@ -13422,55 +13428,77 @@
         <v>13</v>
       </c>
       <c r="B380" s="7">
-        <v>962</v>
+        <v>212</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>90</v>
+        <v>228</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
-      <c r="M380" s="7"/>
+      <c t="s" r="M380" s="7">
+        <v>418</v>
+      </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
-      <c r="A381" s="6"/>
-      <c r="B381" s="7"/>
-      <c r="C381" s="7"/>
+      <c t="s" r="A381" s="6">
+        <v>13</v>
+      </c>
+      <c r="B381" s="7">
+        <v>215</v>
+      </c>
+      <c t="s" r="C381" s="7">
+        <v>14</v>
+      </c>
       <c r="D381" s="7"/>
-      <c r="E381" s="7"/>
-      <c r="F381" s="7"/>
-      <c r="G381" s="8"/>
-      <c r="H381" s="8"/>
-      <c r="I381" s="7"/>
-      <c r="J381" s="7"/>
+      <c t="s" r="E381" s="7">
+        <v>417</v>
+      </c>
+      <c r="F381" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G381" s="8">
+        <v>230</v>
+      </c>
+      <c t="s" r="H381" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I381" s="7">
+        <v>344</v>
+      </c>
+      <c t="s" r="J381" s="7">
+        <v>352</v>
+      </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
-      <c r="M381" s="7"/>
+      <c t="s" r="M381" s="7">
+        <v>419</v>
+      </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
       <c t="s" r="A382" s="6">
         <v>13</v>
       </c>
       <c r="B382" s="7">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
@@ -13486,26 +13514,24 @@
         <v>21</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>118</v>
+        <v>371</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>228</v>
+        <v>84</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
-      <c t="s" r="M382" s="7">
-        <v>418</v>
-      </c>
+      <c r="M382" s="7"/>
     </row>
     <row r="383" ht="14.25" customHeight="1">
       <c t="s" r="A383" s="6">
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>215</v>
+        <v>693</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
@@ -13518,29 +13544,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>344</v>
+        <v>31</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>352</v>
+        <v>222</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
-      <c t="s" r="M383" s="7">
-        <v>419</v>
-      </c>
+      <c r="M383" s="7"/>
     </row>
     <row r="384" ht="14.25" customHeight="1">
       <c t="s" r="A384" s="6">
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>278</v>
+        <v>692</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
@@ -13553,16 +13577,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>120</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>371</v>
+        <v>105</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>84</v>
+        <v>300</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13573,7 +13597,7 @@
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>693</v>
+        <v>926</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
@@ -13589,47 +13613,29 @@
         <v>120</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>272</v>
+        <v>16</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>31</v>
+        <v>420</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>222</v>
+        <v>402</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c r="M385" s="7"/>
     </row>
     <row r="386" ht="14.25" customHeight="1">
-      <c t="s" r="A386" s="6">
-        <v>13</v>
-      </c>
-      <c r="B386" s="7">
-        <v>692</v>
-      </c>
-      <c t="s" r="C386" s="7">
-        <v>14</v>
-      </c>
+      <c r="A386" s="6"/>
+      <c r="B386" s="7"/>
+      <c r="C386" s="7"/>
       <c r="D386" s="7"/>
-      <c t="s" r="E386" s="7">
-        <v>417</v>
-      </c>
-      <c r="F386" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G386" s="8">
-        <v>272</v>
-      </c>
-      <c t="s" r="H386" s="8">
-        <v>120</v>
-      </c>
-      <c t="s" r="I386" s="7">
-        <v>105</v>
-      </c>
-      <c t="s" r="J386" s="7">
-        <v>300</v>
-      </c>
+      <c r="E386" s="7"/>
+      <c r="F386" s="7"/>
+      <c r="G386" s="8"/>
+      <c r="H386" s="8"/>
+      <c r="I386" s="7"/>
+      <c r="J386" s="7"/>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c r="M386" s="7"/>
@@ -13639,45 +13645,65 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H387" s="8">
         <v>120</v>
       </c>
-      <c t="s" r="H387" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I387" s="7">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
-      <c r="M387" s="7"/>
+      <c t="s" r="M387" s="7">
+        <v>48</v>
+      </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c r="A388" s="6"/>
-      <c r="B388" s="7"/>
-      <c r="C388" s="7"/>
+      <c t="s" r="A388" s="6">
+        <v>13</v>
+      </c>
+      <c r="B388" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="C388" s="7">
+        <v>14</v>
+      </c>
       <c r="D388" s="7"/>
-      <c r="E388" s="7"/>
-      <c r="F388" s="7"/>
-      <c r="G388" s="8"/>
-      <c r="H388" s="8"/>
-      <c r="I388" s="7"/>
-      <c r="J388" s="7"/>
+      <c t="s" r="E388" s="7">
+        <v>421</v>
+      </c>
+      <c r="F388" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G388" s="8">
+        <v>120</v>
+      </c>
+      <c t="s" r="H388" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I388" s="7">
+        <v>140</v>
+      </c>
+      <c t="s" r="J388" s="7">
+        <v>310</v>
+      </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
@@ -13687,7 +13713,7 @@
         <v>13</v>
       </c>
       <c r="B389" s="7">
-        <v>925</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C389" s="7">
         <v>14</v>
@@ -13700,29 +13726,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>120</v>
+        <v>391</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>422</v>
+        <v>32</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
-      <c t="s" r="M389" s="7">
-        <v>48</v>
-      </c>
+      <c r="M389" s="7"/>
     </row>
     <row r="390" ht="15" customHeight="1">
       <c t="s" r="A390" s="6">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B390" s="7">
-        <v>279</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
@@ -13735,108 +13759,112 @@
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>120</v>
+        <v>391</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>140</v>
+        <v>423</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>310</v>
+        <v>424</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c r="M390" s="7"/>
     </row>
     <row r="391" ht="14.25" customHeight="1">
-      <c t="s" r="A391" s="6">
-        <v>13</v>
-      </c>
-      <c r="B391" s="7">
-        <v>3900</v>
-      </c>
-      <c t="s" r="C391" s="7">
-        <v>14</v>
-      </c>
+      <c r="A391" s="6"/>
+      <c r="B391" s="7"/>
+      <c r="C391" s="7"/>
       <c r="D391" s="7"/>
-      <c t="s" r="E391" s="7">
-        <v>421</v>
-      </c>
-      <c r="F391" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G391" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H391" s="8">
-        <v>391</v>
-      </c>
-      <c t="s" r="I391" s="7">
-        <v>209</v>
-      </c>
-      <c t="s" r="J391" s="7">
-        <v>32</v>
-      </c>
+      <c r="E391" s="7"/>
+      <c r="F391" s="7"/>
+      <c r="G391" s="8"/>
+      <c r="H391" s="8"/>
+      <c r="I391" s="7"/>
+      <c r="J391" s="7"/>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c r="M391" s="7"/>
     </row>
     <row r="392" ht="14.25" customHeight="1">
       <c t="s" r="A392" s="6">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B392" s="7">
-        <v>3901</v>
+        <v>121</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>391</v>
+        <v>67</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>423</v>
+        <v>247</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>424</v>
+        <v>155</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
-      <c r="M392" s="7"/>
+      <c t="s" r="M392" s="7">
+        <v>317</v>
+      </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
-      <c r="A393" s="6"/>
-      <c r="B393" s="7"/>
-      <c r="C393" s="7"/>
+      <c t="s" r="A393" s="6">
+        <v>13</v>
+      </c>
+      <c r="B393" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="C393" s="7">
+        <v>14</v>
+      </c>
       <c r="D393" s="7"/>
-      <c r="E393" s="7"/>
-      <c r="F393" s="7"/>
-      <c r="G393" s="8"/>
-      <c r="H393" s="8"/>
-      <c r="I393" s="7"/>
-      <c r="J393" s="7"/>
+      <c t="s" r="E393" s="7">
+        <v>425</v>
+      </c>
+      <c r="F393" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G393" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="H393" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I393" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J393" s="7">
+        <v>422</v>
+      </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
-      <c r="M393" s="7"/>
+      <c t="s" r="M393" s="7">
+        <v>426</v>
+      </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
       <c t="s" r="A394" s="6">
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>121</v>
+        <v>330</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
@@ -13849,21 +13877,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>247</v>
+        <v>135</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>155</v>
+        <v>287</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -13871,7 +13899,7 @@
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>321</v>
+        <v>136</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
@@ -13887,26 +13915,24 @@
         <v>21</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
-      <c t="s" r="M395" s="7">
-        <v>426</v>
-      </c>
+      <c r="M395" s="7"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
       <c t="s" r="A396" s="6">
         <v>13</v>
       </c>
       <c r="B396" s="7">
-        <v>330</v>
+        <v>145</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
@@ -13919,16 +13945,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>135</v>
+        <v>289</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>287</v>
+        <v>183</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13939,7 +13965,7 @@
         <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>136</v>
+        <v>331</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
@@ -13955,13 +13981,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>122</v>
+        <v>427</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>414</v>
+        <v>164</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13972,7 +13998,7 @@
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>145</v>
+        <v>328</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
@@ -13985,16 +14011,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>289</v>
+        <v>71</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14005,7 +14031,7 @@
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>331</v>
+        <v>160</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
@@ -14021,47 +14047,29 @@
         <v>21</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>427</v>
+        <v>300</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>164</v>
+        <v>358</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c r="M399" s="7"/>
     </row>
     <row r="400" ht="15" customHeight="1">
-      <c t="s" r="A400" s="6">
-        <v>13</v>
-      </c>
-      <c r="B400" s="7">
-        <v>328</v>
-      </c>
-      <c t="s" r="C400" s="7">
-        <v>14</v>
-      </c>
+      <c r="A400" s="6"/>
+      <c r="B400" s="7"/>
+      <c r="C400" s="7"/>
       <c r="D400" s="7"/>
-      <c t="s" r="E400" s="7">
-        <v>425</v>
-      </c>
-      <c r="F400" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G400" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H400" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="I400" s="7">
-        <v>71</v>
-      </c>
-      <c t="s" r="J400" s="7">
-        <v>209</v>
-      </c>
+      <c r="E400" s="7"/>
+      <c r="F400" s="7"/>
+      <c r="G400" s="8"/>
+      <c r="H400" s="8"/>
+      <c r="I400" s="7"/>
+      <c r="J400" s="7"/>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c r="M400" s="7"/>
@@ -14071,45 +14079,65 @@
         <v>13</v>
       </c>
       <c r="B401" s="7">
-        <v>160</v>
+        <v>801</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F401" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
         <v>21</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>300</v>
+        <v>429</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>358</v>
+        <v>40</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
-      <c r="M401" s="7"/>
+      <c t="s" r="M401" s="7">
+        <v>430</v>
+      </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c r="A402" s="6"/>
-      <c r="B402" s="7"/>
-      <c r="C402" s="7"/>
+      <c t="s" r="A402" s="6">
+        <v>13</v>
+      </c>
+      <c r="B402" s="7">
+        <v>802</v>
+      </c>
+      <c t="s" r="C402" s="7">
+        <v>14</v>
+      </c>
       <c r="D402" s="7"/>
-      <c r="E402" s="7"/>
-      <c r="F402" s="7"/>
-      <c r="G402" s="8"/>
-      <c r="H402" s="8"/>
-      <c r="I402" s="7"/>
-      <c r="J402" s="7"/>
+      <c t="s" r="E402" s="7">
+        <v>428</v>
+      </c>
+      <c r="F402" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G402" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H402" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I402" s="7">
+        <v>287</v>
+      </c>
+      <c t="s" r="J402" s="7">
+        <v>109</v>
+      </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
@@ -14119,7 +14147,7 @@
         <v>13</v>
       </c>
       <c r="B403" s="7">
-        <v>801</v>
+        <v>362</v>
       </c>
       <c t="s" r="C403" s="7">
         <v>14</v>
@@ -14135,26 +14163,24 @@
         <v>21</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>25</v>
+        <v>272</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>429</v>
+        <v>194</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>40</v>
+        <v>202</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
-      <c t="s" r="M403" s="7">
-        <v>430</v>
-      </c>
+      <c r="M403" s="7"/>
     </row>
     <row r="404" ht="14.25" customHeight="1">
       <c t="s" r="A404" s="6">
         <v>13</v>
       </c>
       <c r="B404" s="7">
-        <v>802</v>
+        <v>363</v>
       </c>
       <c t="s" r="C404" s="7">
         <v>14</v>
@@ -14167,16 +14193,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>25</v>
+        <v>272</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14187,7 +14213,7 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>362</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
@@ -14203,13 +14229,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>272</v>
+        <v>398</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14217,10 +14243,10 @@
     </row>
     <row r="406" ht="14.25" customHeight="1">
       <c t="s" r="A406" s="6">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B406" s="7">
-        <v>363</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
@@ -14233,108 +14259,112 @@
         <v>320</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>272</v>
+        <v>398</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c r="M406" s="7"/>
     </row>
     <row r="407" ht="14.25" customHeight="1">
-      <c t="s" r="A407" s="6">
-        <v>13</v>
-      </c>
-      <c r="B407" s="7">
-        <v>3948</v>
-      </c>
-      <c t="s" r="C407" s="7">
-        <v>14</v>
-      </c>
+      <c r="A407" s="6"/>
+      <c r="B407" s="7"/>
+      <c r="C407" s="7"/>
       <c r="D407" s="7"/>
-      <c t="s" r="E407" s="7">
-        <v>428</v>
-      </c>
-      <c r="F407" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G407" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H407" s="8">
-        <v>398</v>
-      </c>
-      <c t="s" r="I407" s="7">
-        <v>85</v>
-      </c>
-      <c t="s" r="J407" s="7">
-        <v>235</v>
-      </c>
+      <c r="E407" s="7"/>
+      <c r="F407" s="7"/>
+      <c r="G407" s="8"/>
+      <c r="H407" s="8"/>
+      <c r="I407" s="7"/>
+      <c r="J407" s="7"/>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c r="M407" s="7"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
       <c t="s" r="A408" s="6">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B408" s="7">
-        <v>3949</v>
+        <v>1242</v>
       </c>
       <c t="s" r="C408" s="7">
         <v>14</v>
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F408" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>388</v>
+        <v>291</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
-      <c r="M408" s="7"/>
+      <c t="s" r="M408" s="7">
+        <v>432</v>
+      </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
-      <c r="A409" s="6"/>
-      <c r="B409" s="7"/>
-      <c r="C409" s="7"/>
+      <c t="s" r="A409" s="6">
+        <v>13</v>
+      </c>
+      <c r="B409" s="7">
+        <v>1241</v>
+      </c>
+      <c t="s" r="C409" s="7">
+        <v>14</v>
+      </c>
       <c r="D409" s="7"/>
-      <c r="E409" s="7"/>
-      <c r="F409" s="7"/>
-      <c r="G409" s="8"/>
-      <c r="H409" s="8"/>
-      <c r="I409" s="7"/>
-      <c r="J409" s="7"/>
+      <c t="s" r="E409" s="7">
+        <v>431</v>
+      </c>
+      <c r="F409" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G409" s="8">
+        <v>297</v>
+      </c>
+      <c t="s" r="H409" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I409" s="7">
+        <v>157</v>
+      </c>
+      <c t="s" r="J409" s="7">
+        <v>172</v>
+      </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
-      <c r="M409" s="7"/>
+      <c t="s" r="M409" s="7">
+        <v>192</v>
+      </c>
     </row>
     <row r="410" ht="15" customHeight="1">
       <c t="s" r="A410" s="6">
         <v>13</v>
       </c>
       <c r="B410" s="7">
-        <v>1242</v>
+        <v>335</v>
       </c>
       <c t="s" r="C410" s="7">
         <v>14</v>
@@ -14350,26 +14380,24 @@
         <v>21</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>297</v>
+        <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>291</v>
+        <v>122</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
-      <c t="s" r="M410" s="7">
-        <v>432</v>
-      </c>
+      <c r="M410" s="7"/>
     </row>
     <row r="411" ht="14.25" customHeight="1">
       <c t="s" r="A411" s="6">
         <v>13</v>
       </c>
       <c r="B411" s="7">
-        <v>1241</v>
+        <v>766</v>
       </c>
       <c t="s" r="C411" s="7">
         <v>14</v>
@@ -14382,29 +14410,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>297</v>
+        <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>157</v>
+        <v>298</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
-      <c t="s" r="M411" s="7">
-        <v>192</v>
-      </c>
+      <c r="M411" s="7"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
       <c t="s" r="A412" s="6">
         <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>335</v>
+        <v>767</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
@@ -14417,16 +14443,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>109</v>
+        <v>310</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14437,7 +14463,7 @@
         <v>13</v>
       </c>
       <c r="B413" s="7">
-        <v>766</v>
+        <v>976</v>
       </c>
       <c t="s" r="C413" s="7">
         <v>14</v>
@@ -14453,47 +14479,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>298</v>
+        <v>100</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>98</v>
+        <v>433</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c r="M413" s="7"/>
     </row>
     <row r="414" ht="14.25" customHeight="1">
-      <c t="s" r="A414" s="6">
-        <v>13</v>
-      </c>
-      <c r="B414" s="7">
-        <v>767</v>
-      </c>
-      <c t="s" r="C414" s="7">
-        <v>14</v>
-      </c>
+      <c r="A414" s="6"/>
+      <c r="B414" s="7"/>
+      <c r="C414" s="7"/>
       <c r="D414" s="7"/>
-      <c t="s" r="E414" s="7">
-        <v>431</v>
-      </c>
-      <c r="F414" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G414" s="8">
-        <v>120</v>
-      </c>
-      <c t="s" r="H414" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I414" s="7">
-        <v>241</v>
-      </c>
-      <c t="s" r="J414" s="7">
-        <v>310</v>
-      </c>
+      <c r="E414" s="7"/>
+      <c r="F414" s="7"/>
+      <c r="G414" s="8"/>
+      <c r="H414" s="8"/>
+      <c r="I414" s="7"/>
+      <c r="J414" s="7"/>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c r="M414" s="7"/>
@@ -14503,128 +14511,148 @@
         <v>13</v>
       </c>
       <c r="B415" s="7">
-        <v>976</v>
+        <v>934</v>
       </c>
       <c t="s" r="C415" s="7">
         <v>14</v>
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>433</v>
+        <v>202</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
-      <c r="M415" s="7"/>
+      <c t="s" r="M415" s="7">
+        <v>435</v>
+      </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
-      <c r="A416" s="6"/>
-      <c r="B416" s="7"/>
-      <c r="C416" s="7"/>
+      <c t="s" r="A416" s="6">
+        <v>13</v>
+      </c>
+      <c r="B416" s="7">
+        <v>935</v>
+      </c>
+      <c t="s" r="C416" s="7">
+        <v>14</v>
+      </c>
       <c r="D416" s="7"/>
-      <c r="E416" s="7"/>
-      <c r="F416" s="7"/>
-      <c r="G416" s="8"/>
-      <c r="H416" s="8"/>
-      <c r="I416" s="7"/>
-      <c r="J416" s="7"/>
+      <c t="s" r="E416" s="7">
+        <v>434</v>
+      </c>
+      <c r="F416" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G416" s="8">
+        <v>66</v>
+      </c>
+      <c t="s" r="H416" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="I416" s="7">
+        <v>31</v>
+      </c>
+      <c t="s" r="J416" s="7">
+        <v>72</v>
+      </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c r="M416" s="7"/>
     </row>
     <row r="417" ht="14.25" customHeight="1">
-      <c t="s" r="A417" s="6">
-        <v>13</v>
-      </c>
-      <c r="B417" s="7">
-        <v>934</v>
-      </c>
-      <c t="s" r="C417" s="7">
-        <v>14</v>
-      </c>
+      <c r="A417" s="6"/>
+      <c r="B417" s="7"/>
+      <c r="C417" s="7"/>
       <c r="D417" s="7"/>
-      <c t="s" r="E417" s="7">
-        <v>434</v>
-      </c>
-      <c r="F417" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G417" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H417" s="8">
-        <v>66</v>
-      </c>
-      <c t="s" r="I417" s="7">
-        <v>179</v>
-      </c>
-      <c t="s" r="J417" s="7">
-        <v>202</v>
-      </c>
+      <c r="E417" s="7"/>
+      <c r="F417" s="7"/>
+      <c r="G417" s="8"/>
+      <c r="H417" s="8"/>
+      <c r="I417" s="7"/>
+      <c r="J417" s="7"/>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
-      <c t="s" r="M417" s="7">
-        <v>435</v>
-      </c>
+      <c r="M417" s="7"/>
     </row>
     <row r="418" ht="14.25" customHeight="1">
       <c t="s" r="A418" s="6">
         <v>13</v>
       </c>
       <c r="B418" s="7">
-        <v>935</v>
+        <v>130</v>
       </c>
       <c t="s" r="C418" s="7">
         <v>14</v>
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>67</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>31</v>
+        <v>220</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
-      <c r="M418" s="7"/>
+      <c t="s" r="M418" s="7">
+        <v>351</v>
+      </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
-      <c r="A419" s="6"/>
-      <c r="B419" s="7"/>
-      <c r="C419" s="7"/>
+      <c t="s" r="A419" s="6">
+        <v>13</v>
+      </c>
+      <c r="B419" s="7">
+        <v>133</v>
+      </c>
+      <c t="s" r="C419" s="7">
+        <v>14</v>
+      </c>
       <c r="D419" s="7"/>
-      <c r="E419" s="7"/>
-      <c r="F419" s="7"/>
-      <c r="G419" s="8"/>
-      <c r="H419" s="8"/>
-      <c r="I419" s="7"/>
-      <c r="J419" s="7"/>
+      <c t="s" r="E419" s="7">
+        <v>436</v>
+      </c>
+      <c r="F419" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G419" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="H419" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I419" s="7">
+        <v>172</v>
+      </c>
+      <c t="s" r="J419" s="7">
+        <v>110</v>
+      </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c r="M419" s="7"/>
@@ -14634,7 +14662,7 @@
         <v>13</v>
       </c>
       <c r="B420" s="7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c t="s" r="C420" s="7">
         <v>14</v>
@@ -14653,23 +14681,21 @@
         <v>67</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>220</v>
+        <v>414</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>171</v>
+        <v>241</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
-      <c t="s" r="M420" s="7">
-        <v>351</v>
-      </c>
+      <c r="M420" s="7"/>
     </row>
     <row r="421" ht="14.25" customHeight="1">
       <c t="s" r="A421" s="6">
         <v>13</v>
       </c>
       <c r="B421" s="7">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c t="s" r="C421" s="7">
         <v>14</v>
@@ -14688,44 +14714,26 @@
         <v>21</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c r="M421" s="7"/>
     </row>
     <row r="422" ht="14.25" customHeight="1">
-      <c t="s" r="A422" s="6">
-        <v>13</v>
-      </c>
-      <c r="B422" s="7">
-        <v>140</v>
-      </c>
-      <c t="s" r="C422" s="7">
-        <v>14</v>
-      </c>
+      <c r="A422" s="6"/>
+      <c r="B422" s="7"/>
+      <c r="C422" s="7"/>
       <c r="D422" s="7"/>
-      <c t="s" r="E422" s="7">
-        <v>436</v>
-      </c>
-      <c r="F422" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G422" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H422" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I422" s="7">
-        <v>414</v>
-      </c>
-      <c t="s" r="J422" s="7">
-        <v>241</v>
-      </c>
+      <c r="E422" s="7"/>
+      <c r="F422" s="7"/>
+      <c r="G422" s="8"/>
+      <c r="H422" s="8"/>
+      <c r="I422" s="7"/>
+      <c r="J422" s="7"/>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c r="M422" s="7"/>
@@ -14735,55 +14743,77 @@
         <v>13</v>
       </c>
       <c r="B423" s="7">
-        <v>151</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C423" s="7">
         <v>14</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F423" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
-      <c r="M423" s="7"/>
+      <c t="s" r="M423" s="7">
+        <v>440</v>
+      </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
-      <c r="A424" s="6"/>
-      <c r="B424" s="7"/>
-      <c r="C424" s="7"/>
+      <c t="s" r="A424" s="6">
+        <v>13</v>
+      </c>
+      <c r="B424" s="7">
+        <v>1373</v>
+      </c>
+      <c t="s" r="C424" s="7">
+        <v>14</v>
+      </c>
       <c r="D424" s="7"/>
-      <c r="E424" s="7"/>
-      <c r="F424" s="7"/>
-      <c r="G424" s="8"/>
-      <c r="H424" s="8"/>
-      <c r="I424" s="7"/>
-      <c r="J424" s="7"/>
+      <c t="s" r="E424" s="7">
+        <v>437</v>
+      </c>
+      <c r="F424" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G424" s="8">
+        <v>438</v>
+      </c>
+      <c t="s" r="H424" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I424" s="7">
+        <v>368</v>
+      </c>
+      <c t="s" r="J424" s="7">
+        <v>22</v>
+      </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
-      <c r="M424" s="7"/>
+      <c t="s" r="M424" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="425" ht="15" customHeight="1">
       <c t="s" r="A425" s="6">
         <v>13</v>
       </c>
       <c r="B425" s="7">
-        <v>1372</v>
+        <v>337</v>
       </c>
       <c t="s" r="C425" s="7">
         <v>14</v>
@@ -14799,18 +14829,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>438</v>
+        <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>439</v>
+        <v>308</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>76</v>
-      </c>
-      <c r="K425" s="7"/>
+        <v>133</v>
+      </c>
+      <c t="s" r="K425" s="7">
+        <v>48</v>
+      </c>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>440</v>
+        <v>192</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -14818,7 +14850,7 @@
         <v>13</v>
       </c>
       <c r="B426" s="7">
-        <v>1373</v>
+        <v>324</v>
       </c>
       <c t="s" r="C426" s="7">
         <v>14</v>
@@ -14831,21 +14863,23 @@
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>438</v>
+        <v>17</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>368</v>
+        <v>171</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>22</v>
-      </c>
-      <c r="K426" s="7"/>
+        <v>136</v>
+      </c>
+      <c t="s" r="K426" s="7">
+        <v>26</v>
+      </c>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>295</v>
+        <v>148</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -14853,7 +14887,7 @@
         <v>13</v>
       </c>
       <c r="B427" s="7">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c t="s" r="C427" s="7">
         <v>14</v>
@@ -14869,20 +14903,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>17</v>
+        <v>438</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>308</v>
+        <v>180</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c t="s" r="K427" s="7">
-        <v>48</v>
+        <v>270</v>
       </c>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>156</v>
+        <v>289</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -14890,7 +14924,7 @@
         <v>13</v>
       </c>
       <c r="B428" s="7">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
@@ -14903,23 +14937,23 @@
         <v>320</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>17</v>
+        <v>438</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>136</v>
+        <v>324</v>
       </c>
       <c t="s" r="K428" s="7">
-        <v>26</v>
+        <v>271</v>
       </c>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>148</v>
+        <v>174</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -14927,7 +14961,7 @@
         <v>13</v>
       </c>
       <c r="B429" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
@@ -14946,25 +14980,21 @@
         <v>438</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>102</v>
-      </c>
-      <c t="s" r="K429" s="7">
-        <v>270</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="K429" s="7"/>
       <c r="L429" s="7"/>
-      <c t="s" r="M429" s="7">
-        <v>289</v>
-      </c>
+      <c r="M429" s="7"/>
     </row>
     <row r="430" ht="15" customHeight="1">
       <c t="s" r="A430" s="6">
         <v>13</v>
       </c>
       <c r="B430" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="C430" s="7">
         <v>14</v>
@@ -14983,48 +15013,26 @@
         <v>21</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>260</v>
+        <v>175</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>324</v>
-      </c>
-      <c t="s" r="K430" s="7">
-        <v>271</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="K430" s="7"/>
       <c r="L430" s="7"/>
-      <c t="s" r="M430" s="7">
-        <v>174</v>
-      </c>
+      <c r="M430" s="7"/>
     </row>
     <row r="431" ht="14.25" customHeight="1">
-      <c t="s" r="A431" s="6">
-        <v>13</v>
-      </c>
-      <c r="B431" s="7">
-        <v>376</v>
-      </c>
-      <c t="s" r="C431" s="7">
-        <v>14</v>
-      </c>
+      <c r="A431" s="6"/>
+      <c r="B431" s="7"/>
+      <c r="C431" s="7"/>
       <c r="D431" s="7"/>
-      <c t="s" r="E431" s="7">
-        <v>437</v>
-      </c>
-      <c r="F431" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G431" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H431" s="8">
-        <v>438</v>
-      </c>
-      <c t="s" r="I431" s="7">
-        <v>310</v>
-      </c>
-      <c t="s" r="J431" s="7">
-        <v>127</v>
-      </c>
+      <c r="E431" s="7"/>
+      <c r="F431" s="7"/>
+      <c r="G431" s="8"/>
+      <c r="H431" s="8"/>
+      <c r="I431" s="7"/>
+      <c r="J431" s="7"/>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c r="M431" s="7"/>
@@ -15034,45 +15042,65 @@
         <v>13</v>
       </c>
       <c r="B432" s="7">
-        <v>377</v>
+        <v>608</v>
       </c>
       <c t="s" r="C432" s="7">
         <v>14</v>
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F432" s="7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
-      <c r="M432" s="7"/>
+      <c t="s" r="M432" s="7">
+        <v>287</v>
+      </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
-      <c r="A433" s="6"/>
-      <c r="B433" s="7"/>
-      <c r="C433" s="7"/>
+      <c t="s" r="A433" s="6">
+        <v>13</v>
+      </c>
+      <c r="B433" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="C433" s="7">
+        <v>14</v>
+      </c>
       <c r="D433" s="7"/>
-      <c r="E433" s="7"/>
-      <c r="F433" s="7"/>
-      <c r="G433" s="8"/>
-      <c r="H433" s="8"/>
-      <c r="I433" s="7"/>
-      <c r="J433" s="7"/>
+      <c t="s" r="E433" s="7">
+        <v>441</v>
+      </c>
+      <c r="F433" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G433" s="8">
+        <v>193</v>
+      </c>
+      <c t="s" r="H433" s="8">
+        <v>442</v>
+      </c>
+      <c t="s" r="I433" s="7">
+        <v>124</v>
+      </c>
+      <c t="s" r="J433" s="7">
+        <v>71</v>
+      </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c r="M433" s="7"/>
@@ -15082,7 +15110,7 @@
         <v>13</v>
       </c>
       <c r="B434" s="7">
-        <v>608</v>
+        <v>68</v>
       </c>
       <c t="s" r="C434" s="7">
         <v>14</v>
@@ -15095,52 +15123,32 @@
         <v>330</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>193</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>303</v>
+        <v>443</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
-      <c t="s" r="M434" s="7">
-        <v>287</v>
-      </c>
+      <c r="M434" s="7"/>
     </row>
     <row r="435" ht="15" customHeight="1">
-      <c t="s" r="A435" s="6">
-        <v>13</v>
-      </c>
-      <c r="B435" s="7">
-        <v>67</v>
-      </c>
-      <c t="s" r="C435" s="7">
-        <v>14</v>
-      </c>
+      <c r="A435" s="6"/>
+      <c r="B435" s="7"/>
+      <c r="C435" s="7"/>
       <c r="D435" s="7"/>
-      <c t="s" r="E435" s="7">
-        <v>441</v>
-      </c>
-      <c r="F435" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G435" s="8">
-        <v>193</v>
-      </c>
-      <c t="s" r="H435" s="8">
-        <v>442</v>
-      </c>
-      <c t="s" r="I435" s="7">
-        <v>124</v>
-      </c>
-      <c t="s" r="J435" s="7">
-        <v>71</v>
-      </c>
+      <c r="E435" s="7"/>
+      <c r="F435" s="7"/>
+      <c r="G435" s="8"/>
+      <c r="H435" s="8"/>
+      <c r="I435" s="7"/>
+      <c r="J435" s="7"/>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c r="M435" s="7"/>
@@ -15150,161 +15158,161 @@
         <v>13</v>
       </c>
       <c r="B436" s="7">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c t="s" r="C436" s="7">
         <v>14</v>
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
-      <c r="M436" s="7"/>
+      <c t="s" r="M436" s="7">
+        <v>446</v>
+      </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
-      <c r="A437" s="6"/>
-      <c r="B437" s="7"/>
-      <c r="C437" s="7"/>
+      <c t="s" r="A437" s="6">
+        <v>13</v>
+      </c>
+      <c r="B437" s="7">
+        <v>85</v>
+      </c>
+      <c t="s" r="C437" s="7">
+        <v>14</v>
+      </c>
       <c r="D437" s="7"/>
-      <c r="E437" s="7"/>
-      <c r="F437" s="7"/>
-      <c r="G437" s="8"/>
-      <c r="H437" s="8"/>
-      <c r="I437" s="7"/>
-      <c r="J437" s="7"/>
+      <c t="s" r="E437" s="7">
+        <v>444</v>
+      </c>
+      <c r="F437" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G437" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="H437" s="8">
+        <v>445</v>
+      </c>
+      <c t="s" r="I437" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J437" s="7">
+        <v>279</v>
+      </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c r="M437" s="7"/>
     </row>
     <row r="438" ht="14.25" customHeight="1">
-      <c t="s" r="A438" s="6">
-        <v>13</v>
-      </c>
-      <c r="B438" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="C438" s="7">
-        <v>14</v>
-      </c>
+      <c r="A438" s="6"/>
+      <c r="B438" s="7"/>
+      <c r="C438" s="7"/>
       <c r="D438" s="7"/>
-      <c t="s" r="E438" s="7">
-        <v>444</v>
-      </c>
-      <c r="F438" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G438" s="8">
-        <v>445</v>
-      </c>
-      <c t="s" r="H438" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="I438" s="7">
-        <v>240</v>
-      </c>
-      <c t="s" r="J438" s="7">
-        <v>324</v>
-      </c>
+      <c r="E438" s="7"/>
+      <c r="F438" s="7"/>
+      <c r="G438" s="8"/>
+      <c r="H438" s="8"/>
+      <c r="I438" s="7"/>
+      <c r="J438" s="7"/>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
-      <c t="s" r="M438" s="7">
-        <v>446</v>
-      </c>
+      <c r="M438" s="7"/>
     </row>
     <row r="439" ht="14.25" customHeight="1">
       <c t="s" r="A439" s="6">
         <v>13</v>
       </c>
       <c r="B439" s="7">
-        <v>85</v>
+        <v>5062</v>
       </c>
       <c t="s" r="C439" s="7">
         <v>14</v>
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c r="M439" s="7"/>
     </row>
     <row r="440" ht="15" customHeight="1">
-      <c r="A440" s="6"/>
-      <c r="B440" s="7"/>
-      <c r="C440" s="7"/>
+      <c t="s" r="A440" s="6">
+        <v>13</v>
+      </c>
+      <c r="B440" s="7">
+        <v>5063</v>
+      </c>
+      <c t="s" r="C440" s="7">
+        <v>14</v>
+      </c>
       <c r="D440" s="7"/>
-      <c r="E440" s="7"/>
-      <c r="F440" s="7"/>
-      <c r="G440" s="8"/>
-      <c r="H440" s="8"/>
-      <c r="I440" s="7"/>
-      <c r="J440" s="7"/>
+      <c t="s" r="E440" s="7">
+        <v>447</v>
+      </c>
+      <c r="F440" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G440" s="8">
+        <v>448</v>
+      </c>
+      <c t="s" r="H440" s="8">
+        <v>193</v>
+      </c>
+      <c t="s" r="I440" s="7">
+        <v>284</v>
+      </c>
+      <c t="s" r="J440" s="7">
+        <v>449</v>
+      </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c r="M440" s="7"/>
     </row>
     <row r="441" ht="14.25" customHeight="1">
-      <c t="s" r="A441" s="6">
-        <v>13</v>
-      </c>
-      <c r="B441" s="7">
-        <v>5062</v>
-      </c>
-      <c t="s" r="C441" s="7">
-        <v>14</v>
-      </c>
+      <c r="A441" s="6"/>
+      <c r="B441" s="7"/>
+      <c r="C441" s="7"/>
       <c r="D441" s="7"/>
-      <c t="s" r="E441" s="7">
-        <v>447</v>
-      </c>
-      <c r="F441" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G441" s="8">
-        <v>193</v>
-      </c>
-      <c t="s" r="H441" s="8">
-        <v>448</v>
-      </c>
-      <c t="s" r="I441" s="7">
-        <v>54</v>
-      </c>
-      <c t="s" r="J441" s="7">
-        <v>152</v>
-      </c>
+      <c r="E441" s="7"/>
+      <c r="F441" s="7"/>
+      <c r="G441" s="8"/>
+      <c r="H441" s="8"/>
+      <c r="I441" s="7"/>
+      <c r="J441" s="7"/>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c r="M441" s="7"/>
@@ -15314,45 +15322,65 @@
         <v>13</v>
       </c>
       <c r="B442" s="7">
-        <v>5063</v>
+        <v>664</v>
       </c>
       <c t="s" r="C442" s="7">
-        <v>14</v>
+        <v>248</v>
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>448</v>
+        <v>17</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>193</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>449</v>
+        <v>254</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
-      <c r="M442" s="7"/>
+      <c t="s" r="M442" s="7">
+        <v>216</v>
+      </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
-      <c r="A443" s="6"/>
-      <c r="B443" s="7"/>
-      <c r="C443" s="7"/>
+      <c t="s" r="A443" s="6">
+        <v>13</v>
+      </c>
+      <c r="B443" s="7">
+        <v>609</v>
+      </c>
+      <c t="s" r="C443" s="7">
+        <v>14</v>
+      </c>
       <c r="D443" s="7"/>
-      <c r="E443" s="7"/>
-      <c r="F443" s="7"/>
-      <c r="G443" s="8"/>
-      <c r="H443" s="8"/>
-      <c r="I443" s="7"/>
-      <c r="J443" s="7"/>
+      <c t="s" r="E443" s="7">
+        <v>450</v>
+      </c>
+      <c r="F443" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G443" s="8">
+        <v>193</v>
+      </c>
+      <c t="s" r="H443" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I443" s="7">
+        <v>172</v>
+      </c>
+      <c t="s" r="J443" s="7">
+        <v>43</v>
+      </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c r="M443" s="7"/>
@@ -15362,10 +15390,10 @@
         <v>13</v>
       </c>
       <c r="B444" s="7">
-        <v>664</v>
+        <v>142</v>
       </c>
       <c t="s" r="C444" s="7">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
@@ -15375,29 +15403,27 @@
         <v>330</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>157</v>
+        <v>270</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
-      <c t="s" r="M444" s="7">
-        <v>216</v>
-      </c>
+      <c r="M444" s="7"/>
     </row>
     <row r="445" ht="15" customHeight="1">
       <c t="s" r="A445" s="6">
         <v>13</v>
       </c>
       <c r="B445" s="7">
-        <v>609</v>
+        <v>193</v>
       </c>
       <c t="s" r="C445" s="7">
         <v>14</v>
@@ -15410,50 +15436,32 @@
         <v>330</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>43</v>
+        <v>299</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c r="M445" s="7"/>
     </row>
     <row r="446" ht="14.25" customHeight="1">
-      <c t="s" r="A446" s="6">
-        <v>13</v>
-      </c>
-      <c r="B446" s="7">
-        <v>142</v>
-      </c>
-      <c t="s" r="C446" s="7">
-        <v>14</v>
-      </c>
+      <c r="A446" s="6"/>
+      <c r="B446" s="7"/>
+      <c r="C446" s="7"/>
       <c r="D446" s="7"/>
-      <c t="s" r="E446" s="7">
-        <v>450</v>
-      </c>
-      <c r="F446" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G446" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H446" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I446" s="7">
-        <v>270</v>
-      </c>
-      <c t="s" r="J446" s="7">
-        <v>202</v>
-      </c>
+      <c r="E446" s="7"/>
+      <c r="F446" s="7"/>
+      <c r="G446" s="8"/>
+      <c r="H446" s="8"/>
+      <c r="I446" s="7"/>
+      <c r="J446" s="7"/>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c r="M446" s="7"/>
@@ -15463,29 +15471,29 @@
         <v>13</v>
       </c>
       <c r="B447" s="7">
-        <v>193</v>
+        <v>1326</v>
       </c>
       <c t="s" r="C447" s="7">
         <v>14</v>
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>31</v>
+        <v>289</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>299</v>
+        <v>163</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15511,78 +15519,78 @@
         <v>13</v>
       </c>
       <c r="B449" s="7">
-        <v>1326</v>
+        <v>32</v>
       </c>
       <c t="s" r="C449" s="7">
         <v>14</v>
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>17</v>
+        <v>453</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>289</v>
+        <v>155</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>163</v>
+        <v>241</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c r="M449" s="7"/>
     </row>
     <row r="450" ht="15" customHeight="1">
-      <c r="A450" s="6"/>
-      <c r="B450" s="7"/>
-      <c r="C450" s="7"/>
+      <c t="s" r="A450" s="6">
+        <v>13</v>
+      </c>
+      <c r="B450" s="7">
+        <v>1125</v>
+      </c>
+      <c t="s" r="C450" s="7">
+        <v>14</v>
+      </c>
       <c r="D450" s="7"/>
-      <c r="E450" s="7"/>
-      <c r="F450" s="7"/>
-      <c r="G450" s="8"/>
-      <c r="H450" s="8"/>
-      <c r="I450" s="7"/>
-      <c r="J450" s="7"/>
+      <c t="s" r="E450" s="7">
+        <v>452</v>
+      </c>
+      <c r="F450" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G450" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="H450" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I450" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J450" s="7">
+        <v>454</v>
+      </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c r="M450" s="7"/>
     </row>
     <row r="451" ht="14.25" customHeight="1">
-      <c t="s" r="A451" s="6">
-        <v>13</v>
-      </c>
-      <c r="B451" s="7">
-        <v>32</v>
-      </c>
-      <c t="s" r="C451" s="7">
-        <v>14</v>
-      </c>
+      <c r="A451" s="6"/>
+      <c r="B451" s="7"/>
+      <c r="C451" s="7"/>
       <c r="D451" s="7"/>
-      <c t="s" r="E451" s="7">
-        <v>452</v>
-      </c>
-      <c r="F451" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G451" s="8">
-        <v>453</v>
-      </c>
-      <c t="s" r="H451" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I451" s="7">
-        <v>155</v>
-      </c>
-      <c t="s" r="J451" s="7">
-        <v>241</v>
-      </c>
+      <c r="E451" s="7"/>
+      <c r="F451" s="7"/>
+      <c r="G451" s="8"/>
+      <c r="H451" s="8"/>
+      <c r="I451" s="7"/>
+      <c r="J451" s="7"/>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c r="M451" s="7"/>
@@ -15592,157 +15600,109 @@
         <v>13</v>
       </c>
       <c r="B452" s="7">
-        <v>1125</v>
+        <v>81</v>
       </c>
       <c t="s" r="C452" s="7">
         <v>14</v>
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>454</v>
+        <v>246</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c r="M452" s="7"/>
     </row>
     <row r="453" ht="14.25" customHeight="1">
-      <c r="A453" s="6"/>
-      <c r="B453" s="7"/>
-      <c r="C453" s="7"/>
+      <c t="s" r="A453" s="6">
+        <v>33</v>
+      </c>
+      <c r="B453" s="7">
+        <v>82</v>
+      </c>
+      <c t="s" r="C453" s="7">
+        <v>14</v>
+      </c>
       <c r="D453" s="7"/>
-      <c r="E453" s="7"/>
-      <c r="F453" s="7"/>
-      <c r="G453" s="8"/>
-      <c r="H453" s="8"/>
-      <c r="I453" s="7"/>
-      <c r="J453" s="7"/>
+      <c t="s" r="E453" s="7">
+        <v>455</v>
+      </c>
+      <c r="F453" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G453" s="8">
+        <v>456</v>
+      </c>
+      <c t="s" r="H453" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I453" s="7">
+        <v>340</v>
+      </c>
+      <c t="s" r="J453" s="7">
+        <v>167</v>
+      </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c r="M453" s="7"/>
     </row>
-    <row r="454" ht="14.25" customHeight="1">
-      <c t="s" r="A454" s="6">
-        <v>13</v>
-      </c>
-      <c r="B454" s="7">
-        <v>81</v>
-      </c>
-      <c t="s" r="C454" s="7">
-        <v>14</v>
-      </c>
-      <c r="D454" s="7"/>
-      <c t="s" r="E454" s="7">
-        <v>455</v>
-      </c>
-      <c r="F454" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G454" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H454" s="8">
-        <v>456</v>
-      </c>
-      <c t="s" r="I454" s="7">
-        <v>41</v>
-      </c>
-      <c t="s" r="J454" s="7">
-        <v>246</v>
-      </c>
-      <c r="K454" s="7"/>
-      <c r="L454" s="7"/>
-      <c r="M454" s="7"/>
-    </row>
-    <row r="455" ht="15" customHeight="1">
-      <c t="s" r="A455" s="6">
-        <v>33</v>
-      </c>
-      <c r="B455" s="7">
-        <v>82</v>
-      </c>
-      <c t="s" r="C455" s="7">
-        <v>14</v>
-      </c>
-      <c r="D455" s="7"/>
-      <c t="s" r="E455" s="7">
-        <v>455</v>
-      </c>
-      <c r="F455" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G455" s="8">
-        <v>456</v>
-      </c>
-      <c t="s" r="H455" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="I455" s="7">
-        <v>340</v>
-      </c>
-      <c t="s" r="J455" s="7">
-        <v>167</v>
-      </c>
-      <c r="K455" s="7"/>
-      <c r="L455" s="7"/>
-      <c r="M455" s="7"/>
-    </row>
-    <row r="456" ht="15.75" customHeight="1">
-      <c t="s" r="A456" s="9">
+    <row r="454" ht="15.75" customHeight="1">
+      <c t="s" r="A454" s="9">
         <v>457</v>
       </c>
-      <c r="B456" s="9"/>
-      <c r="C456" s="9"/>
-      <c r="D456" s="9"/>
-      <c r="E456" s="9"/>
-      <c r="F456" s="9"/>
-      <c r="G456" s="9"/>
-      <c r="H456" s="9"/>
-      <c r="I456" s="9"/>
-      <c r="J456" s="9"/>
-      <c r="K456" s="9"/>
-      <c r="L456" s="9"/>
-      <c r="M456" s="9"/>
-      <c r="N456" s="9"/>
-      <c r="O456" s="9"/>
-    </row>
-    <row r="457" ht="65.25" customHeight="1"/>
-    <row r="458" ht="16.5" customHeight="1">
-      <c t="s" r="A458" s="10">
+      <c r="B454" s="9"/>
+      <c r="C454" s="9"/>
+      <c r="D454" s="9"/>
+      <c r="E454" s="9"/>
+      <c r="F454" s="9"/>
+      <c r="G454" s="9"/>
+      <c r="H454" s="9"/>
+      <c r="I454" s="9"/>
+      <c r="J454" s="9"/>
+      <c r="K454" s="9"/>
+      <c r="L454" s="9"/>
+      <c r="M454" s="9"/>
+      <c r="N454" s="9"/>
+      <c r="O454" s="9"/>
+    </row>
+    <row r="455" ht="66" customHeight="1"/>
+    <row r="456" ht="16.5" customHeight="1">
+      <c t="s" r="A456" s="10">
         <v>458</v>
       </c>
-      <c r="B458" s="10"/>
-      <c r="C458" s="10"/>
-      <c r="D458" s="10"/>
-      <c r="E458" s="10"/>
-      <c r="F458" s="10"/>
-      <c r="G458" s="10"/>
-      <c r="H458" s="10"/>
-      <c r="I458" s="10"/>
-      <c r="J458" s="10"/>
-      <c r="K458" s="10"/>
-      <c t="s" r="L458" s="11">
+      <c r="B456" s="10"/>
+      <c r="C456" s="10"/>
+      <c r="D456" s="10"/>
+      <c r="E456" s="10"/>
+      <c r="F456" s="10"/>
+      <c r="G456" s="10"/>
+      <c r="H456" s="10"/>
+      <c r="I456" s="10"/>
+      <c r="J456" s="10"/>
+      <c r="K456" s="10"/>
+      <c t="s" r="L456" s="11">
         <v>459</v>
       </c>
-      <c r="M458" s="11"/>
-      <c r="N458" s="11"/>
+      <c r="M456" s="11"/>
+      <c r="N456" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="906">
+  <mergeCells count="902">
     <mergeCell ref="D1:O1"/>
     <mergeCell ref="D2:O2"/>
     <mergeCell ref="D3:O4"/>
@@ -16642,13 +16602,9 @@
     <mergeCell ref="K452:L452"/>
     <mergeCell ref="C453:D453"/>
     <mergeCell ref="K453:L453"/>
-    <mergeCell ref="C454:D454"/>
-    <mergeCell ref="K454:L454"/>
-    <mergeCell ref="C455:D455"/>
-    <mergeCell ref="K455:L455"/>
-    <mergeCell ref="A456:O456"/>
-    <mergeCell ref="A458:K458"/>
-    <mergeCell ref="L458:N458"/>
+    <mergeCell ref="A454:O454"/>
+    <mergeCell ref="A456:K456"/>
+    <mergeCell ref="L456:N456"/>
   </mergeCells>
   <pageMargins left="0.196666672825813" right="0.219999998807907" top="0.280000001192093" bottom="0.230000004172325" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
